--- a/artfynd/A 42890-2025 artfynd.xlsx
+++ b/artfynd/A 42890-2025 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>82647904</v>
       </c>
       <c r="B2" t="n">
-        <v>96354</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98600</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>613134.8503166767</v>
+        <v>613135</v>
       </c>
       <c r="R2" t="n">
-        <v>6887468.813919707</v>
+        <v>6887469</v>
       </c>
       <c r="S2" t="n">
         <v>100</v>
@@ -753,19 +748,9 @@
           <t>1984-07-20</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>1984-07-20</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -804,12 +789,7 @@
         <v>82647903</v>
       </c>
       <c r="B3" t="n">
-        <v>96367</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98613</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -841,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>613134.8503166767</v>
+        <v>613135</v>
       </c>
       <c r="R3" t="n">
-        <v>6887468.813919707</v>
+        <v>6887469</v>
       </c>
       <c r="S3" t="n">
         <v>100</v>
@@ -879,19 +859,9 @@
           <t>1984-07-20</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>1984-07-20</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -930,12 +900,7 @@
         <v>82647916</v>
       </c>
       <c r="B4" t="n">
-        <v>95522</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97457</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -967,10 +932,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>613134.8503166767</v>
+        <v>613135</v>
       </c>
       <c r="R4" t="n">
-        <v>6887468.813919707</v>
+        <v>6887469</v>
       </c>
       <c r="S4" t="n">
         <v>100</v>
@@ -1005,19 +970,9 @@
           <t>1984-07-20</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>1984-07-20</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1056,12 +1011,7 @@
         <v>82647892</v>
       </c>
       <c r="B5" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100761</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1093,10 +1043,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>613134.8503166767</v>
+        <v>613135</v>
       </c>
       <c r="R5" t="n">
-        <v>6887468.813919707</v>
+        <v>6887469</v>
       </c>
       <c r="S5" t="n">
         <v>100</v>
@@ -1131,19 +1081,9 @@
           <t>1984-07-20</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>1984-07-20</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1182,12 +1122,7 @@
         <v>82647907</v>
       </c>
       <c r="B6" t="n">
-        <v>96252</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98497</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1219,10 +1154,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>613134.8503166767</v>
+        <v>613135</v>
       </c>
       <c r="R6" t="n">
-        <v>6887468.813919707</v>
+        <v>6887469</v>
       </c>
       <c r="S6" t="n">
         <v>100</v>
@@ -1257,19 +1192,9 @@
           <t>1984-07-20</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>1984-07-20</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1308,12 +1233,7 @@
         <v>82647905</v>
       </c>
       <c r="B7" t="n">
-        <v>96312</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98557</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1345,10 +1265,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>613134.8503166767</v>
+        <v>613135</v>
       </c>
       <c r="R7" t="n">
-        <v>6887468.813919707</v>
+        <v>6887469</v>
       </c>
       <c r="S7" t="n">
         <v>100</v>
@@ -1383,19 +1303,9 @@
           <t>1984-07-20</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>1984-07-20</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1434,12 +1344,7 @@
         <v>82647917</v>
       </c>
       <c r="B8" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97454</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1471,10 +1376,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>613134.8503166767</v>
+        <v>613135</v>
       </c>
       <c r="R8" t="n">
-        <v>6887468.813919707</v>
+        <v>6887469</v>
       </c>
       <c r="S8" t="n">
         <v>100</v>
@@ -1509,19 +1414,9 @@
           <t>1984-07-20</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>1984-07-20</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 42890-2025 artfynd.xlsx
+++ b/artfynd/A 42890-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>82647904</v>
       </c>
       <c r="B2" t="n">
-        <v>98600</v>
+        <v>98606</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>82647903</v>
       </c>
       <c r="B3" t="n">
-        <v>98613</v>
+        <v>98619</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>82647916</v>
       </c>
       <c r="B4" t="n">
-        <v>97457</v>
+        <v>97463</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>82647892</v>
       </c>
       <c r="B5" t="n">
-        <v>100761</v>
+        <v>100768</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>82647907</v>
       </c>
       <c r="B6" t="n">
-        <v>98497</v>
+        <v>98503</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>82647905</v>
       </c>
       <c r="B7" t="n">
-        <v>98557</v>
+        <v>98563</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>82647917</v>
       </c>
       <c r="B8" t="n">
-        <v>97454</v>
+        <v>97460</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 42890-2025 artfynd.xlsx
+++ b/artfynd/A 42890-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>82647904</v>
       </c>
       <c r="B2" t="n">
-        <v>98606</v>
+        <v>98609</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>82647903</v>
       </c>
       <c r="B3" t="n">
-        <v>98619</v>
+        <v>98622</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>82647916</v>
       </c>
       <c r="B4" t="n">
-        <v>97463</v>
+        <v>97465</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>82647892</v>
       </c>
       <c r="B5" t="n">
-        <v>100768</v>
+        <v>100773</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>82647907</v>
       </c>
       <c r="B6" t="n">
-        <v>98503</v>
+        <v>98506</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>82647905</v>
       </c>
       <c r="B7" t="n">
-        <v>98563</v>
+        <v>98566</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>82647917</v>
       </c>
       <c r="B8" t="n">
-        <v>97460</v>
+        <v>97462</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 42890-2025 artfynd.xlsx
+++ b/artfynd/A 42890-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>82647904</v>
       </c>
       <c r="B2" t="n">
-        <v>98609</v>
+        <v>98612</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>82647903</v>
       </c>
       <c r="B3" t="n">
-        <v>98622</v>
+        <v>98625</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>82647892</v>
       </c>
       <c r="B5" t="n">
-        <v>100773</v>
+        <v>100779</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>82647907</v>
       </c>
       <c r="B6" t="n">
-        <v>98506</v>
+        <v>98509</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>82647905</v>
       </c>
       <c r="B7" t="n">
-        <v>98566</v>
+        <v>98569</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 42890-2025 artfynd.xlsx
+++ b/artfynd/A 42890-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>82647904</v>
       </c>
       <c r="B2" t="n">
-        <v>98612</v>
+        <v>98613</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>82647903</v>
       </c>
       <c r="B3" t="n">
-        <v>98625</v>
+        <v>98626</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>82647916</v>
       </c>
       <c r="B4" t="n">
-        <v>97465</v>
+        <v>97466</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>82647892</v>
       </c>
       <c r="B5" t="n">
-        <v>100779</v>
+        <v>100780</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>82647907</v>
       </c>
       <c r="B6" t="n">
-        <v>98509</v>
+        <v>98510</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>82647905</v>
       </c>
       <c r="B7" t="n">
-        <v>98569</v>
+        <v>98570</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>82647917</v>
       </c>
       <c r="B8" t="n">
-        <v>97462</v>
+        <v>97463</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 42890-2025 artfynd.xlsx
+++ b/artfynd/A 42890-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>82647904</v>
       </c>
       <c r="B2" t="n">
-        <v>98613</v>
+        <v>98640</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>82647903</v>
       </c>
       <c r="B3" t="n">
-        <v>98626</v>
+        <v>98653</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>82647916</v>
       </c>
       <c r="B4" t="n">
-        <v>97466</v>
+        <v>97493</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>82647892</v>
       </c>
       <c r="B5" t="n">
-        <v>100780</v>
+        <v>100807</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>82647907</v>
       </c>
       <c r="B6" t="n">
-        <v>98510</v>
+        <v>98537</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>82647905</v>
       </c>
       <c r="B7" t="n">
-        <v>98570</v>
+        <v>98597</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>82647917</v>
       </c>
       <c r="B8" t="n">
-        <v>97463</v>
+        <v>97490</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 42890-2025 artfynd.xlsx
+++ b/artfynd/A 42890-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>82647904</v>
       </c>
       <c r="B2" t="n">
-        <v>98640</v>
+        <v>98646</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>82647903</v>
       </c>
       <c r="B3" t="n">
-        <v>98653</v>
+        <v>98659</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>82647916</v>
       </c>
       <c r="B4" t="n">
-        <v>97493</v>
+        <v>97499</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>82647892</v>
       </c>
       <c r="B5" t="n">
-        <v>100807</v>
+        <v>100813</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>82647907</v>
       </c>
       <c r="B6" t="n">
-        <v>98537</v>
+        <v>98543</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>82647905</v>
       </c>
       <c r="B7" t="n">
-        <v>98597</v>
+        <v>98603</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>82647917</v>
       </c>
       <c r="B8" t="n">
-        <v>97490</v>
+        <v>97496</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 42890-2025 artfynd.xlsx
+++ b/artfynd/A 42890-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>82647904</v>
       </c>
       <c r="B2" t="n">
-        <v>98646</v>
+        <v>98653</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>82647903</v>
       </c>
       <c r="B3" t="n">
-        <v>98659</v>
+        <v>98666</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>82647916</v>
       </c>
       <c r="B4" t="n">
-        <v>97499</v>
+        <v>97506</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>82647892</v>
       </c>
       <c r="B5" t="n">
-        <v>100813</v>
+        <v>100820</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>82647907</v>
       </c>
       <c r="B6" t="n">
-        <v>98543</v>
+        <v>98550</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>82647905</v>
       </c>
       <c r="B7" t="n">
-        <v>98603</v>
+        <v>98610</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>82647917</v>
       </c>
       <c r="B8" t="n">
-        <v>97496</v>
+        <v>97503</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 42890-2025 artfynd.xlsx
+++ b/artfynd/A 42890-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>82647904</v>
       </c>
       <c r="B2" t="n">
-        <v>98653</v>
+        <v>98657</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>82647903</v>
       </c>
       <c r="B3" t="n">
-        <v>98666</v>
+        <v>98670</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>82647916</v>
       </c>
       <c r="B4" t="n">
-        <v>97506</v>
+        <v>97510</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>82647892</v>
       </c>
       <c r="B5" t="n">
-        <v>100820</v>
+        <v>100824</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>82647907</v>
       </c>
       <c r="B6" t="n">
-        <v>98550</v>
+        <v>98554</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>82647905</v>
       </c>
       <c r="B7" t="n">
-        <v>98610</v>
+        <v>98614</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>82647917</v>
       </c>
       <c r="B8" t="n">
-        <v>97503</v>
+        <v>97507</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 42890-2025 artfynd.xlsx
+++ b/artfynd/A 42890-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>82647904</v>
       </c>
       <c r="B2" t="n">
-        <v>98657</v>
+        <v>98664</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>82647903</v>
       </c>
       <c r="B3" t="n">
-        <v>98670</v>
+        <v>98677</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>82647916</v>
       </c>
       <c r="B4" t="n">
-        <v>97510</v>
+        <v>97517</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>82647892</v>
       </c>
       <c r="B5" t="n">
-        <v>100824</v>
+        <v>100831</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>82647907</v>
       </c>
       <c r="B6" t="n">
-        <v>98554</v>
+        <v>98561</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>82647905</v>
       </c>
       <c r="B7" t="n">
-        <v>98614</v>
+        <v>98621</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>82647917</v>
       </c>
       <c r="B8" t="n">
-        <v>97507</v>
+        <v>97514</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 42890-2025 artfynd.xlsx
+++ b/artfynd/A 42890-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>82647904</v>
       </c>
       <c r="B2" t="n">
-        <v>98667</v>
+        <v>98672</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>82647903</v>
       </c>
       <c r="B3" t="n">
-        <v>98680</v>
+        <v>98685</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>82647916</v>
       </c>
       <c r="B4" t="n">
-        <v>97520</v>
+        <v>97525</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>82647892</v>
       </c>
       <c r="B5" t="n">
-        <v>100834</v>
+        <v>100839</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>82647907</v>
       </c>
       <c r="B6" t="n">
-        <v>98564</v>
+        <v>98569</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>82647905</v>
       </c>
       <c r="B7" t="n">
-        <v>98624</v>
+        <v>98629</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>82647917</v>
       </c>
       <c r="B8" t="n">
-        <v>97517</v>
+        <v>97522</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 42890-2025 artfynd.xlsx
+++ b/artfynd/A 42890-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>82647904</v>
       </c>
       <c r="B2" t="n">
-        <v>98672</v>
+        <v>98680</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>82647903</v>
       </c>
       <c r="B3" t="n">
-        <v>98685</v>
+        <v>98693</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>82647916</v>
       </c>
       <c r="B4" t="n">
-        <v>97525</v>
+        <v>97533</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>82647892</v>
       </c>
       <c r="B5" t="n">
-        <v>100839</v>
+        <v>100847</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>82647907</v>
       </c>
       <c r="B6" t="n">
-        <v>98569</v>
+        <v>98577</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>82647905</v>
       </c>
       <c r="B7" t="n">
-        <v>98629</v>
+        <v>98637</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>82647917</v>
       </c>
       <c r="B8" t="n">
-        <v>97522</v>
+        <v>97530</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
